--- a/productos/07-control-ventas/Control-de-Ventas.xlsx
+++ b/productos/07-control-ventas/Control-de-Ventas.xlsx
@@ -124,7 +124,7 @@
     <t xml:space="preserve">7. Celdas protegidas</t>
   </si>
   <si>
-    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Contraseña de desprotección: plantilla2026.</t>
+    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Si necesitas editar otra celda, ve a Revisar → Desproteger hoja (no pide contraseña).</t>
   </si>
   <si>
     <t xml:space="preserve">Soporte y otras plantillas de esta línea de productos: www.tumarca.com</t>
@@ -1571,11 +1571,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="92251180"/>
-        <c:axId val="43833270"/>
+        <c:axId val="6172630"/>
+        <c:axId val="48136596"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="92251180"/>
+        <c:axId val="6172630"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1607,7 +1607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43833270"/>
+        <c:crossAx val="48136596"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1615,7 +1615,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43833270"/>
+        <c:axId val="48136596"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1657,7 +1657,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92251180"/>
+        <c:crossAx val="6172630"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1867,11 +1867,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="57355649"/>
-        <c:axId val="59258520"/>
+        <c:axId val="12684823"/>
+        <c:axId val="65478354"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57355649"/>
+        <c:axId val="12684823"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1903,7 +1903,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59258520"/>
+        <c:crossAx val="65478354"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1911,7 +1911,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59258520"/>
+        <c:axId val="65478354"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1953,7 +1953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57355649"/>
+        <c:crossAx val="12684823"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2455,7 +2455,7 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="16">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:F6"/>
@@ -2594,7 +2594,7 @@
       <c r="C25" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="16">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
@@ -2750,7 +2750,7 @@
       <c r="D14" s="20"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B14:D14"/>
@@ -2880,7 +2880,7 @@
       <c r="C12" s="22"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="1">
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -2976,7 +2976,7 @@
       <c r="B11" s="21"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
   </mergeCells>
@@ -6401,7 +6401,7 @@
       <c r="H204" s="21"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
@@ -6896,7 +6896,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="5">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
@@ -7001,7 +7001,7 @@
       <c r="I7" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="10">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
